--- a/data/trans_orig/P33A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P33A-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que las horas que duerme le permiten descansar lo suficiente en 2012</t>
+          <t>Población que las horas que duerme le permiten descansar lo suficiente en 2012 (tasa de respuesta: 99,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>583918</t>
+          <t>585820</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>620453</t>
+          <t>621641</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>471350</t>
+          <t>468696</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>519725</t>
+          <t>518045</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1065652</t>
+          <t>1069386</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1128973</t>
+          <t>1131260</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,24%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79952</t>
+          <t>78764</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>116487</t>
+          <t>114585</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>172373</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>220748</t>
+          <t>223402</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>263531</t>
+          <t>261244</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>326852</t>
+          <t>323118</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,2%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>828197</t>
+          <t>826940</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>876575</t>
+          <t>878799</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>735741</t>
+          <t>736889</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>793761</t>
+          <t>793502</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1584799</t>
+          <t>1578675</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1659210</t>
+          <t>1656567</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,08%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>136347</t>
+          <t>134123</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>184725</t>
+          <t>185982</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>236382</t>
+          <t>236641</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>294402</t>
+          <t>293254</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>383855</t>
+          <t>386498</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>458266</t>
+          <t>464390</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,73%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>615539</t>
+          <t>613681</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>655347</t>
+          <t>654358</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>542218</t>
+          <t>541436</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>594154</t>
+          <t>596499</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1170455</t>
+          <t>1172859</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1237428</t>
+          <t>1240246</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,36%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>96968</t>
+          <t>97957</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>136776</t>
+          <t>138634</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>177936</t>
+          <t>175591</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>229872</t>
+          <t>230654</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>286977</t>
+          <t>284159</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>353950</t>
+          <t>351546</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,06%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>768616</t>
+          <t>767812</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>816009</t>
+          <t>813896</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>730475</t>
+          <t>733363</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>786500</t>
+          <t>791268</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1517405</t>
+          <t>1514442</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1590173</t>
+          <t>1588646</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,5%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>119986</t>
+          <t>122099</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>167379</t>
+          <t>168183</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>250942</t>
+          <t>246174</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>306967</t>
+          <t>304079</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>383264</t>
+          <t>384791</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>456032</t>
+          <t>458995</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,26%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2846952</t>
+          <t>2845639</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2930374</t>
+          <t>2929184</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2533864</t>
+          <t>2541286</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2643192</t>
+          <t>2650275</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5407116</t>
+          <t>5409254</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5548949</t>
+          <t>5550043</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,05%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>471264</t>
+          <t>472454</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>554686</t>
+          <t>555999</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>888582</t>
+          <t>881499</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>997910</t>
+          <t>990488</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1384463</t>
+          <t>1383369</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1526296</t>
+          <t>1524158</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que las horas que duerme le permiten descansar lo suficiente en 2016</t>
+          <t>Población que las horas que duerme le permiten descansar lo suficiente en 2016 (tasa de respuesta: 98,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>543136</t>
+          <t>546540</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>583108</t>
+          <t>585885</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>464245</t>
+          <t>464755</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>510738</t>
+          <t>511195</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1020426</t>
+          <t>1021579</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1080349</t>
+          <t>1080363</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86856</t>
+          <t>84079</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>126828</t>
+          <t>123424</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>155222</t>
+          <t>154765</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>201715</t>
+          <t>201205</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>255575</t>
+          <t>255561</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>315498</t>
+          <t>314345</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>827023</t>
+          <t>828884</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>875540</t>
+          <t>875527</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>711408</t>
+          <t>713111</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>769122</t>
+          <t>767227</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1554279</t>
+          <t>1556348</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1633230</t>
+          <t>1631747</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,48%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>127043</t>
+          <t>127056</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>175560</t>
+          <t>173699</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>255697</t>
+          <t>257592</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>313411</t>
+          <t>311708</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>394172</t>
+          <t>395655</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>473123</t>
+          <t>471054</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>637533</t>
+          <t>638341</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>676842</t>
+          <t>675816</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>580380</t>
+          <t>580376</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>626319</t>
+          <t>627090</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1231068</t>
+          <t>1231797</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1291148</t>
+          <t>1291702</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,1%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81759</t>
+          <t>82785</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>121068</t>
+          <t>120260</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>150962</t>
+          <t>150191</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>196901</t>
+          <t>196905</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>244734</t>
+          <t>244180</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>304814</t>
+          <t>304085</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,8%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>722494</t>
+          <t>722498</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>772495</t>
+          <t>773731</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>716957</t>
+          <t>714023</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>776565</t>
+          <t>774417</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1456517</t>
+          <t>1456911</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1530722</t>
+          <t>1532098</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,31%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>154122</t>
+          <t>152886</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>204123</t>
+          <t>204119</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>253330</t>
+          <t>255478</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>312938</t>
+          <t>315872</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>425790</t>
+          <t>424414</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>499995</t>
+          <t>499601</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,54%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2780307</t>
+          <t>2781398</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2867078</t>
+          <t>2867936</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2518655</t>
+          <t>2525687</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2629061</t>
+          <t>2631907</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5332697</t>
+          <t>5337494</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5473929</t>
+          <t>5476983</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>79,89%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>490686</t>
+          <t>489828</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>577457</t>
+          <t>576366</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>868894</t>
+          <t>866048</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>979300</t>
+          <t>972268</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1381790</t>
+          <t>1378736</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1523022</t>
+          <t>1518225</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que las horas que duerme le permiten descansar lo suficiente en 2023</t>
+          <t>Población que las horas que duerme le permiten descansar lo suficiente en 2023 (tasa de respuesta: 99,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>513926</t>
+          <t>514366</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>549420</t>
+          <t>550514</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>486711</t>
+          <t>488127</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>522893</t>
+          <t>523334</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1009113</t>
+          <t>1015687</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1061740</t>
+          <t>1066456</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,58%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83999</t>
+          <t>82905</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>119493</t>
+          <t>119053</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>150869</t>
+          <t>150428</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>187051</t>
+          <t>185635</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>245441</t>
+          <t>240725</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>298068</t>
+          <t>291494</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>970707</t>
+          <t>968780</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1103018</t>
+          <t>1102410</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>686848</t>
+          <t>683917</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>731839</t>
+          <t>730849</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1665389</t>
+          <t>1668447</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1860679</t>
+          <t>1869300</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>87,3%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>85417</t>
+          <t>86025</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>217728</t>
+          <t>219655</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>220844</t>
+          <t>221834</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>265835</t>
+          <t>268766</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>280439</t>
+          <t>271818</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>475729</t>
+          <t>472671</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>551952</t>
+          <t>552969</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>596126</t>
+          <t>596972</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>692029</t>
+          <t>691753</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>829421</t>
+          <t>830605</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1269234</t>
+          <t>1268025</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1421014</t>
+          <t>1417432</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,27%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>104081</t>
+          <t>103235</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>148255</t>
+          <t>147238</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>94576</t>
+          <t>93392</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>231968</t>
+          <t>232244</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>203189</t>
+          <t>206771</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>354969</t>
+          <t>356178</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>721497</t>
+          <t>723632</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>771333</t>
+          <t>771192</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>777446</t>
+          <t>774797</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>867528</t>
+          <t>864233</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1516983</t>
+          <t>1519382</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1612489</t>
+          <t>1610350</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,32%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>150045</t>
+          <t>150186</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>199881</t>
+          <t>197746</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>216056</t>
+          <t>219351</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>306138</t>
+          <t>308787</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>392474</t>
+          <t>394613</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>487980</t>
+          <t>485581</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2815441</t>
+          <t>2817174</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3019981</t>
+          <t>3008245</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2701516</t>
+          <t>2698962</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2958545</t>
+          <t>2930686</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5531279</t>
+          <t>5548185</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5816066</t>
+          <t>5831254</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,39%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>423458</t>
+          <t>435194</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>627998</t>
+          <t>626265</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>675481</t>
+          <t>703340</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>932510</t>
+          <t>935064</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1261399</t>
+          <t>1246211</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1546186</t>
+          <t>1529280</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,61%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P33A-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>585820</t>
+          <t>584500</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>621641</t>
+          <t>621673</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>468696</t>
+          <t>468198</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>518045</t>
+          <t>519273</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1069386</t>
+          <t>1067498</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1131260</t>
+          <t>1128598</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,05%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78764</t>
+          <t>78732</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>114585</t>
+          <t>115905</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>174053</t>
+          <t>172825</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>223402</t>
+          <t>223900</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>261244</t>
+          <t>263906</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>323118</t>
+          <t>325006</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>826940</t>
+          <t>827960</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>878799</t>
+          <t>878131</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>736889</t>
+          <t>737279</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>793502</t>
+          <t>796661</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1578675</t>
+          <t>1583067</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1656567</t>
+          <t>1662099</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,35%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>134123</t>
+          <t>134791</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>185982</t>
+          <t>184962</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>236641</t>
+          <t>233482</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>293254</t>
+          <t>292864</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>386498</t>
+          <t>380966</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>464390</t>
+          <t>459998</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,52%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>613681</t>
+          <t>615101</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>654358</t>
+          <t>655733</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>541436</t>
+          <t>542669</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>596499</t>
+          <t>592096</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1172859</t>
+          <t>1172144</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1240246</t>
+          <t>1234863</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,01%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97957</t>
+          <t>96582</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>138634</t>
+          <t>137214</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>175591</t>
+          <t>179994</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>230654</t>
+          <t>229421</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>284159</t>
+          <t>289542</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>351546</t>
+          <t>352261</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>767812</t>
+          <t>767419</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>813896</t>
+          <t>814178</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>733363</t>
+          <t>731839</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>791268</t>
+          <t>790270</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1514442</t>
+          <t>1514180</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1588646</t>
+          <t>1589166</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,53%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>122099</t>
+          <t>121817</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>168183</t>
+          <t>168576</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>246174</t>
+          <t>247172</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>304079</t>
+          <t>305603</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>384791</t>
+          <t>384271</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>458995</t>
+          <t>459257</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,27%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2845639</t>
+          <t>2839887</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2929184</t>
+          <t>2926110</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2541286</t>
+          <t>2535855</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2650275</t>
+          <t>2647044</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5409254</t>
+          <t>5410910</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5550043</t>
+          <t>5545467</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>79,98%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>472454</t>
+          <t>475528</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>555999</t>
+          <t>561751</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>881499</t>
+          <t>884730</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>990488</t>
+          <t>995919</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1383369</t>
+          <t>1387945</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1524158</t>
+          <t>1522502</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>546540</t>
+          <t>546456</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>585885</t>
+          <t>585002</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>464755</t>
+          <t>463034</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>511195</t>
+          <t>509133</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1021579</t>
+          <t>1020123</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1080363</t>
+          <t>1079139</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,78%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84079</t>
+          <t>84962</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>123424</t>
+          <t>123508</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>154765</t>
+          <t>156827</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>201205</t>
+          <t>202926</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>255561</t>
+          <t>256785</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>314345</t>
+          <t>315801</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>828884</t>
+          <t>827628</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>875527</t>
+          <t>874880</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>713111</t>
+          <t>712187</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>767227</t>
+          <t>769402</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1556348</t>
+          <t>1554666</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1631747</t>
+          <t>1634027</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,6%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>127056</t>
+          <t>127703</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>173699</t>
+          <t>174955</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>257592</t>
+          <t>255417</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>311708</t>
+          <t>312632</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>395655</t>
+          <t>393375</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>471054</t>
+          <t>472736</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>638341</t>
+          <t>635587</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>675816</t>
+          <t>675684</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>580376</t>
+          <t>578813</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>627090</t>
+          <t>625992</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1231797</t>
+          <t>1231528</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1291702</t>
+          <t>1292819</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,17%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82785</t>
+          <t>82917</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>120260</t>
+          <t>123014</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>150191</t>
+          <t>151289</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>196905</t>
+          <t>198468</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>244180</t>
+          <t>243063</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>304085</t>
+          <t>304354</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>722498</t>
+          <t>722818</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>773731</t>
+          <t>772068</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>714023</t>
+          <t>712841</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>774417</t>
+          <t>773814</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1456911</t>
+          <t>1458123</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1532098</t>
+          <t>1533540</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,38%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>152886</t>
+          <t>154549</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>204119</t>
+          <t>203799</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>255478</t>
+          <t>256081</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>315872</t>
+          <t>317054</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>424414</t>
+          <t>422972</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>499601</t>
+          <t>498389</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,47%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2781398</t>
+          <t>2782116</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2867936</t>
+          <t>2866482</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2525687</t>
+          <t>2519415</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2631907</t>
+          <t>2626052</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5337494</t>
+          <t>5338511</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5476983</t>
+          <t>5475874</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,87%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>489828</t>
+          <t>491282</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>576366</t>
+          <t>575648</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>866048</t>
+          <t>871903</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>972268</t>
+          <t>978540</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1378736</t>
+          <t>1379845</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1518225</t>
+          <t>1517208</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -4621,32 +4621,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>533160</t>
+          <t>580132</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>514366</t>
+          <t>558242</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>550514</t>
+          <t>598187</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4656,32 +4656,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>506181</t>
+          <t>546090</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>488127</t>
+          <t>527117</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>523334</t>
+          <t>564862</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4691,32 +4691,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1039341</t>
+          <t>1126222</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1015687</t>
+          <t>1097608</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1066456</t>
+          <t>1152266</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,17%</t>
         </is>
       </c>
     </row>
@@ -4734,32 +4734,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>100259</t>
+          <t>108449</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82905</t>
+          <t>90394</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>119053</t>
+          <t>130339</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4769,32 +4769,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>167581</t>
+          <t>184964</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>150428</t>
+          <t>166192</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>185635</t>
+          <t>203937</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>267840</t>
+          <t>293413</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>240725</t>
+          <t>267369</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>291494</t>
+          <t>322027</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -4847,17 +4847,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>633419</t>
+          <t>688581</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>633419</t>
+          <t>688581</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>633419</t>
+          <t>688581</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4882,17 +4882,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>673762</t>
+          <t>731054</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>673762</t>
+          <t>731054</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>673762</t>
+          <t>731054</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1307181</t>
+          <t>1419635</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1307181</t>
+          <t>1419635</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1307181</t>
+          <t>1419635</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4964,32 +4964,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1023303</t>
+          <t>875593</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>968780</t>
+          <t>851094</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1102410</t>
+          <t>900772</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4999,32 +4999,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>709133</t>
+          <t>796733</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>683917</t>
+          <t>770950</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>730849</t>
+          <t>819992</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5034,32 +5034,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1732436</t>
+          <t>1672326</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1668447</t>
+          <t>1636496</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1869300</t>
+          <t>1707441</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>80,95%</t>
         </is>
       </c>
     </row>
@@ -5077,32 +5077,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>165132</t>
+          <t>168586</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>86025</t>
+          <t>143407</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>219655</t>
+          <t>193085</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5112,32 +5112,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>243550</t>
+          <t>268371</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>221834</t>
+          <t>245112</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>268766</t>
+          <t>294154</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>408682</t>
+          <t>436957</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>271818</t>
+          <t>401842</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>472671</t>
+          <t>472787</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -5190,17 +5190,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1188435</t>
+          <t>1044179</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1188435</t>
+          <t>1044179</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1188435</t>
+          <t>1044179</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5225,17 +5225,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>952683</t>
+          <t>1065104</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>952683</t>
+          <t>1065104</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>952683</t>
+          <t>1065104</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5260,17 +5260,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2141118</t>
+          <t>2109283</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2141118</t>
+          <t>2109283</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2141118</t>
+          <t>2109283</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5307,32 +5307,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>575231</t>
+          <t>660434</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>552969</t>
+          <t>635604</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>596972</t>
+          <t>684101</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5342,32 +5342,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>751230</t>
+          <t>599842</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>691753</t>
+          <t>577834</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>830605</t>
+          <t>622783</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5377,32 +5377,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1326460</t>
+          <t>1260275</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1268025</t>
+          <t>1227108</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1417432</t>
+          <t>1293033</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>80,78%</t>
         </is>
       </c>
     </row>
@@ -5420,32 +5420,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>124976</t>
+          <t>137662</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>103235</t>
+          <t>113995</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>147238</t>
+          <t>162492</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5455,32 +5455,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>172767</t>
+          <t>202651</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93392</t>
+          <t>179710</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>232244</t>
+          <t>224659</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>297743</t>
+          <t>340313</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>206771</t>
+          <t>307555</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>356178</t>
+          <t>373480</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>23,33%</t>
         </is>
       </c>
     </row>
@@ -5533,17 +5533,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>700207</t>
+          <t>798096</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>700207</t>
+          <t>798096</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>700207</t>
+          <t>798096</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>923997</t>
+          <t>802493</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>923997</t>
+          <t>802493</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>923997</t>
+          <t>802493</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5603,17 +5603,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1624203</t>
+          <t>1600588</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1624203</t>
+          <t>1600588</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1624203</t>
+          <t>1600588</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5650,17 +5650,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>747487</t>
+          <t>799133</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>723632</t>
+          <t>773561</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>771192</t>
+          <t>826983</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>809159</t>
+          <t>799008</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>774797</t>
+          <t>771738</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>864233</t>
+          <t>822850</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1556647</t>
+          <t>1598141</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1519382</t>
+          <t>1561411</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1610350</t>
+          <t>1633550</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>78,01%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>173891</t>
+          <t>185869</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>150186</t>
+          <t>158019</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>197746</t>
+          <t>211441</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5798,32 +5798,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>274425</t>
+          <t>309961</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>219351</t>
+          <t>286119</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>308787</t>
+          <t>337231</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>448316</t>
+          <t>495830</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>394613</t>
+          <t>460421</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>485581</t>
+          <t>532560</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -5876,17 +5876,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>921378</t>
+          <t>985002</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>921378</t>
+          <t>985002</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>921378</t>
+          <t>985002</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5911,17 +5911,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1083584</t>
+          <t>1108969</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1083584</t>
+          <t>1108969</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1083584</t>
+          <t>1108969</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2004963</t>
+          <t>2093971</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2004963</t>
+          <t>2093971</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2004963</t>
+          <t>2093971</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2879182</t>
+          <t>2915291</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2817174</t>
+          <t>2862662</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3008245</t>
+          <t>2963252</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2775703</t>
+          <t>2741673</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2698962</t>
+          <t>2694831</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2930686</t>
+          <t>2785051</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5654885</t>
+          <t>5656964</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5548185</t>
+          <t>5593634</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5831254</t>
+          <t>5724172</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>79,24%</t>
         </is>
       </c>
     </row>
@@ -6106,32 +6106,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>564257</t>
+          <t>600567</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>435194</t>
+          <t>552606</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>626265</t>
+          <t>653196</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6141,32 +6141,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>858323</t>
+          <t>965947</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>703340</t>
+          <t>922569</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>935064</t>
+          <t>1012789</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1422580</t>
+          <t>1566514</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1246211</t>
+          <t>1499306</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1529280</t>
+          <t>1629844</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,56%</t>
         </is>
       </c>
     </row>
@@ -6219,17 +6219,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3443439</t>
+          <t>3515858</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3443439</t>
+          <t>3515858</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3443439</t>
+          <t>3515858</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6254,17 +6254,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3634026</t>
+          <t>3707620</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3634026</t>
+          <t>3707620</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3634026</t>
+          <t>3707620</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6289,17 +6289,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7077465</t>
+          <t>7223478</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7077465</t>
+          <t>7223478</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7077465</t>
+          <t>7223478</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
